--- a/priv/norm_templates/IT4.xlsx
+++ b/priv/norm_templates/IT4.xlsx
@@ -206,6 +206,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1306,7 +1309,7 @@
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1610,6 +1613,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2271,11 +2278,11 @@
       <c r="S6" s="94"/>
       <c r="T6" s="94"/>
       <c r="U6" s="94"/>
-      <c r="V6" s="64"/>
+      <c r="V6" s="95"/>
       <c r="W6" s="64"/>
       <c r="X6" s="64"/>
       <c r="Y6" s="64"/>
-      <c r="Z6" s="64"/>
+      <c r="Z6" s="95"/>
       <c r="AA6" s="64"/>
       <c r="AB6" s="65"/>
       <c r="AD6" s="10" t="s">
